--- a/stories/arbres/TREE-LAN-005.xlsx
+++ b/stories/arbres/TREE-LAN-005.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1163,7 +1180,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Ava tient la main de papa au marché. Ça sent les pommes. Papa dit : on va nommer. On va classer. Les fruits ensemble. Les habits ensemble. Les jouets ensemble. Chaque groupe est une catégorie. Ava écoute. Elle a envie d'aider.</t>
+          <t>Ava tient la main de papa au marché. Ça sent les pommes. On va nommer. On va classer. Les fruits ensemble. Les habits ensemble. Les jouets ensemble. Chaque groupe est une catégorie. Ava écoute. Elle a envie d'aider.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1301,6 +1318,13 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Ava tient la main de papa au marché. Ça sent les pommes.
+papa|On va nommer. On va classer.
+narrateur|Les fruits ensemble. Les habits ensemble. Les jouets ensemble. Chaque groupe est une catégorie. Ava écoute. Elle a envie d'aider.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1491,6 +1515,11 @@
           <t>prompt réécrit pour coller aux options</t>
         </is>
       </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre l'étal des fruits, l'étal des habits, ou le stand des jouets.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1515,7 +1544,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Ava s'arrête à l'étal des fruits. Une poire. Une fraise. Une pêche. Papa dit : fruits. C'est une catégorie. Ava les nomme. Elle les classe ensemble.</t>
+          <t>Ava s'arrête à l'étal des fruits. Une poire. Une fraise. Une pêche. Fruits. C'est une catégorie. Ava les nomme. Elle les classe ensemble.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1653,6 +1682,13 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Ava s'arrête à l'étal des fruits. Une poire. Une fraise. Une pêche.
+papa|Fruits. C'est une catégorie.
+narrateur|Ava les nomme. Elle les classe ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1829,6 +1865,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Les fruits sont ensemble. Que fait Ava ?</t>
         </is>
       </c>
     </row>
@@ -1997,6 +2038,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Ava a classé les fruits. Une catégorie.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2183,6 +2229,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le panier, la caisse, ou le sac.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2207,7 +2258,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Ava pose les fruits dans le panier. Elle dit : catégorie des fruits. Papa compte : un, deux, trois.</t>
+          <t>Ava pose les fruits dans le panier. Catégorie des fruits. Papa compte : un, deux, trois.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -2345,6 +2396,12 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Ava pose les fruits dans le panier.
+narrateur|Catégorie des fruits. Papa compte : un, deux, trois.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2531,6 +2588,11 @@
         <v>8</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la pomme, la chaussette, ou le cube.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2555,7 +2617,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Ava montre la pomme. Elle dit : fruits, c'est une catégorie. Elle a classé à l'étal des fruits, dans le panier. Papa dit merci.</t>
+          <t>Ava montre la pomme. Fruits, c'est une catégorie. Elle a classé à l'étal des fruits, dans le panier. Papa dit merci.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -2693,6 +2755,12 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Ava montre la pomme.
+narrateur|Fruits, c'est une catégorie. Elle a classé à l'étal des fruits, dans le panier. Papa dit merci.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2855,6 +2923,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -2879,7 +2952,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Ava montre la chaussette. Elle dit : fruits, c'est une catégorie. Elle a classé à l'étal des fruits, dans le panier. Papa dit merci.</t>
+          <t>Ava montre la chaussette. Fruits, c'est une catégorie. Elle a classé à l'étal des fruits, dans le panier. Papa dit merci.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -3017,6 +3090,12 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Ava montre la chaussette.
+narrateur|Fruits, c'est une catégorie. Elle a classé à l'étal des fruits, dans le panier. Papa dit merci.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3179,6 +3258,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3203,7 +3287,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Ava montre le cube. Elle dit : fruits, c'est une catégorie. Elle a classé à l'étal des fruits, dans le panier. Papa dit merci.</t>
+          <t>Ava montre le cube. Fruits, c'est une catégorie. Elle a classé à l'étal des fruits, dans le panier. Papa dit merci.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3341,6 +3425,12 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Ava montre le cube.
+narrateur|Fruits, c'est une catégorie. Elle a classé à l'étal des fruits, dans le panier. Papa dit merci.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3503,6 +3593,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3665,6 +3760,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Ava glisse les fruits dans la caisse. Elle nomme. Elle classe. C'est une catégorie.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3851,6 +3951,11 @@
         <v>8</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la pomme, la chaussette, ou le cube.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -3875,7 +3980,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Ava montre la pomme. Elle dit : fruits, c'est une catégorie. Elle a classé à l'étal des fruits, dans la caisse. Papa dit merci.</t>
+          <t>Ava montre la pomme. Fruits, c'est une catégorie. Elle a classé à l'étal des fruits, dans la caisse. Papa dit merci.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -4013,6 +4118,12 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Ava montre la pomme.
+narrateur|Fruits, c'est une catégorie. Elle a classé à l'étal des fruits, dans la caisse. Papa dit merci.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4175,6 +4286,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4199,7 +4315,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Ava montre la chaussette. Elle dit : fruits, c'est une catégorie. Elle a classé à l'étal des fruits, dans la caisse. Papa dit merci.</t>
+          <t>Ava montre la chaussette. Fruits, c'est une catégorie. Elle a classé à l'étal des fruits, dans la caisse. Papa dit merci.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -4337,6 +4453,12 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Ava montre la chaussette.
+narrateur|Fruits, c'est une catégorie. Elle a classé à l'étal des fruits, dans la caisse. Papa dit merci.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4499,6 +4621,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4523,7 +4650,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Ava montre le cube. Elle dit : fruits, c'est une catégorie. Elle a classé à l'étal des fruits, dans la caisse. Papa dit merci.</t>
+          <t>Ava montre le cube. Fruits, c'est une catégorie. Elle a classé à l'étal des fruits, dans la caisse. Papa dit merci.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -4661,6 +4788,12 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Ava montre le cube.
+narrateur|Fruits, c'est une catégorie. Elle a classé à l'étal des fruits, dans la caisse. Papa dit merci.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4823,6 +4956,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4985,6 +5123,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Ava met les fruits dans le sac. Le sac est souple. Catégorie des fruits.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5171,6 +5314,11 @@
         <v>8</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la pomme, la chaussette, ou le cube.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5195,7 +5343,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Ava montre la pomme. Elle dit : fruits, c'est une catégorie. Elle a classé à l'étal des fruits, dans le sac. Papa dit merci.</t>
+          <t>Ava montre la pomme. Fruits, c'est une catégorie. Elle a classé à l'étal des fruits, dans le sac. Papa dit merci.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -5333,6 +5481,12 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Ava montre la pomme.
+narrateur|Fruits, c'est une catégorie. Elle a classé à l'étal des fruits, dans le sac. Papa dit merci.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5495,6 +5649,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5519,7 +5678,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Ava montre la chaussette. Elle dit : fruits, c'est une catégorie. Elle a classé à l'étal des fruits, dans le sac. Papa dit merci.</t>
+          <t>Ava montre la chaussette. Fruits, c'est une catégorie. Elle a classé à l'étal des fruits, dans le sac. Papa dit merci.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -5657,6 +5816,12 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Ava montre la chaussette.
+narrateur|Fruits, c'est une catégorie. Elle a classé à l'étal des fruits, dans le sac. Papa dit merci.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5819,6 +5984,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5843,7 +6013,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Ava montre le cube. Elle dit : fruits, c'est une catégorie. Elle a classé à l'étal des fruits, dans le sac. Papa dit merci.</t>
+          <t>Ava montre le cube. Fruits, c'est une catégorie. Elle a classé à l'étal des fruits, dans le sac. Papa dit merci.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -5981,6 +6151,12 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Ava montre le cube.
+narrateur|Fruits, c'est une catégorie. Elle a classé à l'étal des fruits, dans le sac. Papa dit merci.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6143,6 +6319,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6167,7 +6348,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Ava s'arrête à l'étal des habits. Un bonnet. Une chaussette. Un gant. Papa dit : habits. C'est une catégorie. Ava les met ensemble.</t>
+          <t>Ava s'arrête à l'étal des habits. Un bonnet. Une chaussette. Un gant. Habits. C'est une catégorie. Ava les met ensemble.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6305,6 +6486,13 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Ava s'arrête à l'étal des habits. Un bonnet. Une chaussette. Un gant.
+papa|Habits. C'est une catégorie.
+narrateur|Ava les met ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6481,6 +6669,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Les habits sont ensemble. Que fait Ava ?</t>
         </is>
       </c>
     </row>
@@ -6649,6 +6842,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Ava a classé les habits. Une catégorie.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6837,6 +7035,11 @@
       <c r="AV35" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le panier, la caisse, ou le sac.</t>
         </is>
       </c>
     </row>
@@ -7001,6 +7204,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Ava plie le bonnet dans le panier. Habits. Une catégorie. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7187,6 +7395,11 @@
         <v>8</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la pomme, la chaussette, ou le cube.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7211,7 +7424,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Ava montre la pomme. Elle dit : habits, c'est une catégorie. Elle a classé à l'étal des habits, dans le panier. Papa dit merci.</t>
+          <t>Ava montre la pomme. Habits, c'est une catégorie. Elle a classé à l'étal des habits, dans le panier. Papa dit merci.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -7349,6 +7562,12 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Ava montre la pomme.
+narrateur|Habits, c'est une catégorie. Elle a classé à l'étal des habits, dans le panier. Papa dit merci.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7511,6 +7730,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7535,7 +7759,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Ava montre la chaussette. Elle dit : habits, c'est une catégorie. Elle a classé à l'étal des habits, dans le panier. Papa dit merci.</t>
+          <t>Ava montre la chaussette. Habits, c'est une catégorie. Elle a classé à l'étal des habits, dans le panier. Papa dit merci.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -7673,6 +7897,12 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Ava montre la chaussette.
+narrateur|Habits, c'est une catégorie. Elle a classé à l'étal des habits, dans le panier. Papa dit merci.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7835,6 +8065,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -7859,7 +8094,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Ava montre le cube. Elle dit : habits, c'est une catégorie. Elle a classé à l'étal des habits, dans le panier. Papa dit merci.</t>
+          <t>Ava montre le cube. Habits, c'est une catégorie. Elle a classé à l'étal des habits, dans le panier. Papa dit merci.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -7997,6 +8232,12 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Ava montre le cube.
+narrateur|Habits, c'est une catégorie. Elle a classé à l'étal des habits, dans le panier. Papa dit merci.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8159,6 +8400,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8321,6 +8567,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Ava pose les chaussettes dans la caisse. Elle classe. Catégorie des habits.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8507,6 +8758,11 @@
         <v>8</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la pomme, la chaussette, ou le cube.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8531,7 +8787,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Ava montre la pomme. Elle dit : habits, c'est une catégorie. Elle a classé à l'étal des habits, dans la caisse. Papa dit merci.</t>
+          <t>Ava montre la pomme. Habits, c'est une catégorie. Elle a classé à l'étal des habits, dans la caisse. Papa dit merci.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -8669,6 +8925,12 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Ava montre la pomme.
+narrateur|Habits, c'est une catégorie. Elle a classé à l'étal des habits, dans la caisse. Papa dit merci.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8831,6 +9093,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -8855,7 +9122,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Ava montre la chaussette. Elle dit : habits, c'est une catégorie. Elle a classé à l'étal des habits, dans la caisse. Papa dit merci.</t>
+          <t>Ava montre la chaussette. Habits, c'est une catégorie. Elle a classé à l'étal des habits, dans la caisse. Papa dit merci.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -8993,6 +9260,12 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Ava montre la chaussette.
+narrateur|Habits, c'est une catégorie. Elle a classé à l'étal des habits, dans la caisse. Papa dit merci.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9155,6 +9428,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9179,7 +9457,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Ava montre le cube. Elle dit : habits, c'est une catégorie. Elle a classé à l'étal des habits, dans la caisse. Papa dit merci.</t>
+          <t>Ava montre le cube. Habits, c'est une catégorie. Elle a classé à l'étal des habits, dans la caisse. Papa dit merci.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -9317,6 +9595,12 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Ava montre le cube.
+narrateur|Habits, c'est une catégorie. Elle a classé à l'étal des habits, dans la caisse. Papa dit merci.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9479,6 +9763,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9641,6 +9930,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Ava glisse le gant dans le sac. Elle nomme. Elle classe. Une catégorie.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9827,6 +10121,11 @@
         <v>8</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la pomme, la chaussette, ou le cube.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9851,7 +10150,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Ava montre la pomme. Elle dit : habits, c'est une catégorie. Elle a classé à l'étal des habits, dans le sac. Papa dit merci.</t>
+          <t>Ava montre la pomme. Habits, c'est une catégorie. Elle a classé à l'étal des habits, dans le sac. Papa dit merci.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -9989,6 +10288,12 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Ava montre la pomme.
+narrateur|Habits, c'est une catégorie. Elle a classé à l'étal des habits, dans le sac. Papa dit merci.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10151,6 +10456,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10175,7 +10485,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Ava montre la chaussette. Elle dit : habits, c'est une catégorie. Elle a classé à l'étal des habits, dans le sac. Papa dit merci.</t>
+          <t>Ava montre la chaussette. Habits, c'est une catégorie. Elle a classé à l'étal des habits, dans le sac. Papa dit merci.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -10313,6 +10623,12 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Ava montre la chaussette.
+narrateur|Habits, c'est une catégorie. Elle a classé à l'étal des habits, dans le sac. Papa dit merci.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10475,6 +10791,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10499,7 +10820,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Ava montre le cube. Elle dit : habits, c'est une catégorie. Elle a classé à l'étal des habits, dans le sac. Papa dit merci.</t>
+          <t>Ava montre le cube. Habits, c'est une catégorie. Elle a classé à l'étal des habits, dans le sac. Papa dit merci.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -10637,6 +10958,12 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Ava montre le cube.
+narrateur|Habits, c'est une catégorie. Elle a classé à l'étal des habits, dans le sac. Papa dit merci.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10799,6 +11126,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10823,7 +11155,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Ava s'arrête au stand des jouets. Un cube. Une balle. Un livre. Papa dit : jouets. C'est une catégorie. Ava les classe ensemble.</t>
+          <t>Ava s'arrête au stand des jouets. Un cube. Une balle. Un livre. Jouets. C'est une catégorie. Ava les classe ensemble.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -10961,6 +11293,13 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Ava s'arrête au stand des jouets. Un cube. Une balle. Un livre.
+papa|Jouets. C'est une catégorie.
+narrateur|Ava les classe ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11137,6 +11476,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Les jouets sont ensemble. Que fait Ava ?</t>
         </is>
       </c>
     </row>
@@ -11305,6 +11649,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Ava a classé les jouets. Une catégorie.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11493,6 +11842,11 @@
       <c r="AV63" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le panier, la caisse, ou le sac.</t>
         </is>
       </c>
     </row>
@@ -11657,6 +12011,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Ava met le cube dans le panier. Jouets. Une catégorie. Le bois est lisse.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11843,6 +12202,11 @@
         <v>8</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la pomme, la chaussette, ou le cube.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -11867,7 +12231,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Ava montre la pomme. Elle dit : jouets, c'est une catégorie. Elle a classé à le stand des jouets, dans le panier. Papa dit merci.</t>
+          <t>Ava montre la pomme. Jouets, c'est une catégorie. Elle a classé à le stand des jouets, dans le panier. Papa dit merci.</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -12005,6 +12369,12 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Ava montre la pomme.
+narrateur|Jouets, c'est une catégorie. Elle a classé à le stand des jouets, dans le panier. Papa dit merci.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12167,6 +12537,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12191,7 +12566,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Ava montre la chaussette. Elle dit : jouets, c'est une catégorie. Elle a classé à le stand des jouets, dans le panier. Papa dit merci.</t>
+          <t>Ava montre la chaussette. Jouets, c'est une catégorie. Elle a classé à le stand des jouets, dans le panier. Papa dit merci.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -12329,6 +12704,12 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Ava montre la chaussette.
+narrateur|Jouets, c'est une catégorie. Elle a classé à le stand des jouets, dans le panier. Papa dit merci.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12491,6 +12872,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12515,7 +12901,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Ava montre le cube. Elle dit : jouets, c'est une catégorie. Elle a classé à le stand des jouets, dans le panier. Papa dit merci.</t>
+          <t>Ava montre le cube. Jouets, c'est une catégorie. Elle a classé à le stand des jouets, dans le panier. Papa dit merci.</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -12653,6 +13039,12 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Ava montre le cube.
+narrateur|Jouets, c'est une catégorie. Elle a classé à le stand des jouets, dans le panier. Papa dit merci.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12815,6 +13207,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12977,6 +13374,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Ava pose la balle dans la caisse. Elle classe. Catégorie des jouets.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13163,6 +13565,11 @@
         <v>8</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la pomme, la chaussette, ou le cube.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13187,7 +13594,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Ava montre la pomme. Elle dit : jouets, c'est une catégorie. Elle a classé à le stand des jouets, dans la caisse. Papa dit merci.</t>
+          <t>Ava montre la pomme. Jouets, c'est une catégorie. Elle a classé à le stand des jouets, dans la caisse. Papa dit merci.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -13325,6 +13732,12 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Ava montre la pomme.
+narrateur|Jouets, c'est une catégorie. Elle a classé à le stand des jouets, dans la caisse. Papa dit merci.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13487,6 +13900,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13511,7 +13929,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Ava montre la chaussette. Elle dit : jouets, c'est une catégorie. Elle a classé à le stand des jouets, dans la caisse. Papa dit merci.</t>
+          <t>Ava montre la chaussette. Jouets, c'est une catégorie. Elle a classé à le stand des jouets, dans la caisse. Papa dit merci.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -13649,6 +14067,12 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Ava montre la chaussette.
+narrateur|Jouets, c'est une catégorie. Elle a classé à le stand des jouets, dans la caisse. Papa dit merci.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13811,6 +14235,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13835,7 +14264,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Ava montre le cube. Elle dit : jouets, c'est une catégorie. Elle a classé à le stand des jouets, dans la caisse. Papa dit merci.</t>
+          <t>Ava montre le cube. Jouets, c'est une catégorie. Elle a classé à le stand des jouets, dans la caisse. Papa dit merci.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -13973,6 +14402,12 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Ava montre le cube.
+narrateur|Jouets, c'est une catégorie. Elle a classé à le stand des jouets, dans la caisse. Papa dit merci.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14135,6 +14570,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14297,6 +14737,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Ava glisse le livre dans le sac. Elle nomme. Elle classe. Une catégorie.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14483,6 +14928,11 @@
         <v>8</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la pomme, la chaussette, ou le cube.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14507,7 +14957,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Ava montre la pomme. Elle dit : jouets, c'est une catégorie. Elle a classé à le stand des jouets, dans le sac. Papa dit merci.</t>
+          <t>Ava montre la pomme. Jouets, c'est une catégorie. Elle a classé à le stand des jouets, dans le sac. Papa dit merci.</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -14645,6 +15095,12 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Ava montre la pomme.
+narrateur|Jouets, c'est une catégorie. Elle a classé à le stand des jouets, dans le sac. Papa dit merci.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14807,6 +15263,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14831,7 +15292,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Ava montre la chaussette. Elle dit : jouets, c'est une catégorie. Elle a classé à le stand des jouets, dans le sac. Papa dit merci.</t>
+          <t>Ava montre la chaussette. Jouets, c'est une catégorie. Elle a classé à le stand des jouets, dans le sac. Papa dit merci.</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -14969,6 +15430,12 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Ava montre la chaussette.
+narrateur|Jouets, c'est une catégorie. Elle a classé à le stand des jouets, dans le sac. Papa dit merci.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15131,6 +15598,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15155,7 +15627,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Ava montre le cube. Elle dit : jouets, c'est une catégorie. Elle a classé à le stand des jouets, dans le sac. Papa dit merci.</t>
+          <t>Ava montre le cube. Jouets, c'est une catégorie. Elle a classé à le stand des jouets, dans le sac. Papa dit merci.</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -15293,6 +15765,12 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Ava montre le cube.
+narrateur|Jouets, c'est une catégorie. Elle a classé à le stand des jouets, dans le sac. Papa dit merci.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15455,6 +15933,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15473,7 +15956,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A4"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15504,6 +15987,13 @@
       <c r="A4" t="inlineStr">
         <is>
           <t>ch2C: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-LAN-005.xlsx
+++ b/stories/arbres/TREE-LAN-005.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1325,6 +1330,7 @@
 narrateur|Les fruits ensemble. Les habits ensemble. Les jouets ensemble. Chaque groupe est une catégorie. Ava écoute. Elle a envie d'aider.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1520,6 +1526,7 @@
           <t>narrateur|On peut prendre l'étal des fruits, l'étal des habits, ou le stand des jouets.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1689,6 +1696,7 @@
 narrateur|Ava les nomme. Elle les classe ensemble.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1872,6 +1880,7 @@
           <t>narrateur|Les fruits sont ensemble. Que fait Ava ?</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2043,6 +2052,7 @@
           <t>narrateur|Ava a classé les fruits. Une catégorie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2234,6 +2244,7 @@
           <t>narrateur|On peut prendre le panier, la caisse, ou le sac.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2402,6 +2413,7 @@
 narrateur|Catégorie des fruits. Papa compte : un, deux, trois.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2593,6 +2605,7 @@
           <t>narrateur|On peut prendre la pomme, la chaussette, ou le cube.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2761,6 +2774,7 @@
 narrateur|Fruits, c'est une catégorie. Elle a classé à l'étal des fruits, dans le panier. Papa dit merci.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2928,6 +2942,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3096,6 +3111,7 @@
 narrateur|Fruits, c'est une catégorie. Elle a classé à l'étal des fruits, dans le panier. Papa dit merci.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3263,6 +3279,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3431,6 +3448,7 @@
 narrateur|Fruits, c'est une catégorie. Elle a classé à l'étal des fruits, dans le panier. Papa dit merci.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3598,6 +3616,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3765,6 +3784,7 @@
           <t>narrateur|Ava glisse les fruits dans la caisse. Elle nomme. Elle classe. C'est une catégorie.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3956,6 +3976,7 @@
           <t>narrateur|On peut prendre la pomme, la chaussette, ou le cube.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4124,6 +4145,7 @@
 narrateur|Fruits, c'est une catégorie. Elle a classé à l'étal des fruits, dans la caisse. Papa dit merci.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4291,6 +4313,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4459,6 +4482,7 @@
 narrateur|Fruits, c'est une catégorie. Elle a classé à l'étal des fruits, dans la caisse. Papa dit merci.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4626,6 +4650,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4794,6 +4819,7 @@
 narrateur|Fruits, c'est une catégorie. Elle a classé à l'étal des fruits, dans la caisse. Papa dit merci.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4961,6 +4987,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5128,6 +5155,7 @@
           <t>narrateur|Ava met les fruits dans le sac. Le sac est souple. Catégorie des fruits.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5319,6 +5347,7 @@
           <t>narrateur|On peut prendre la pomme, la chaussette, ou le cube.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5487,6 +5516,7 @@
 narrateur|Fruits, c'est une catégorie. Elle a classé à l'étal des fruits, dans le sac. Papa dit merci.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5654,6 +5684,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5822,6 +5853,7 @@
 narrateur|Fruits, c'est une catégorie. Elle a classé à l'étal des fruits, dans le sac. Papa dit merci.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5989,6 +6021,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6157,6 +6190,7 @@
 narrateur|Fruits, c'est une catégorie. Elle a classé à l'étal des fruits, dans le sac. Papa dit merci.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6324,6 +6358,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6493,6 +6528,7 @@
 narrateur|Ava les met ensemble.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6676,6 +6712,7 @@
           <t>narrateur|Les habits sont ensemble. Que fait Ava ?</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6847,6 +6884,7 @@
           <t>narrateur|Ava a classé les habits. Une catégorie.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7042,6 +7080,7 @@
           <t>narrateur|On peut prendre le panier, la caisse, ou le sac.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7209,6 +7248,7 @@
           <t>narrateur|Ava plie le bonnet dans le panier. Habits. Une catégorie. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7400,6 +7440,7 @@
           <t>narrateur|On peut prendre la pomme, la chaussette, ou le cube.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7568,6 +7609,7 @@
 narrateur|Habits, c'est une catégorie. Elle a classé à l'étal des habits, dans le panier. Papa dit merci.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7735,6 +7777,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7903,6 +7946,7 @@
 narrateur|Habits, c'est une catégorie. Elle a classé à l'étal des habits, dans le panier. Papa dit merci.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8070,6 +8114,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8238,6 +8283,7 @@
 narrateur|Habits, c'est une catégorie. Elle a classé à l'étal des habits, dans le panier. Papa dit merci.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8405,6 +8451,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8572,6 +8619,7 @@
           <t>narrateur|Ava pose les chaussettes dans la caisse. Elle classe. Catégorie des habits.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8763,6 +8811,7 @@
           <t>narrateur|On peut prendre la pomme, la chaussette, ou le cube.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8931,6 +8980,7 @@
 narrateur|Habits, c'est une catégorie. Elle a classé à l'étal des habits, dans la caisse. Papa dit merci.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9098,6 +9148,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9266,6 +9317,7 @@
 narrateur|Habits, c'est une catégorie. Elle a classé à l'étal des habits, dans la caisse. Papa dit merci.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9433,6 +9485,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9601,6 +9654,7 @@
 narrateur|Habits, c'est une catégorie. Elle a classé à l'étal des habits, dans la caisse. Papa dit merci.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9768,6 +9822,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9935,6 +9990,7 @@
           <t>narrateur|Ava glisse le gant dans le sac. Elle nomme. Elle classe. Une catégorie.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10126,6 +10182,7 @@
           <t>narrateur|On peut prendre la pomme, la chaussette, ou le cube.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10294,6 +10351,7 @@
 narrateur|Habits, c'est une catégorie. Elle a classé à l'étal des habits, dans le sac. Papa dit merci.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10461,6 +10519,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10629,6 +10688,7 @@
 narrateur|Habits, c'est une catégorie. Elle a classé à l'étal des habits, dans le sac. Papa dit merci.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10796,6 +10856,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10964,6 +11025,7 @@
 narrateur|Habits, c'est une catégorie. Elle a classé à l'étal des habits, dans le sac. Papa dit merci.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11131,6 +11193,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11300,6 +11363,7 @@
 narrateur|Ava les classe ensemble.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11483,6 +11547,7 @@
           <t>narrateur|Les jouets sont ensemble. Que fait Ava ?</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11654,6 +11719,7 @@
           <t>narrateur|Ava a classé les jouets. Une catégorie.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11849,6 +11915,7 @@
           <t>narrateur|On peut prendre le panier, la caisse, ou le sac.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12016,6 +12083,7 @@
           <t>narrateur|Ava met le cube dans le panier. Jouets. Une catégorie. Le bois est lisse.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12207,6 +12275,7 @@
           <t>narrateur|On peut prendre la pomme, la chaussette, ou le cube.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12375,6 +12444,7 @@
 narrateur|Jouets, c'est une catégorie. Elle a classé à le stand des jouets, dans le panier. Papa dit merci.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12542,6 +12612,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12710,6 +12781,7 @@
 narrateur|Jouets, c'est une catégorie. Elle a classé à le stand des jouets, dans le panier. Papa dit merci.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12877,6 +12949,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13045,6 +13118,7 @@
 narrateur|Jouets, c'est une catégorie. Elle a classé à le stand des jouets, dans le panier. Papa dit merci.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13212,6 +13286,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13379,6 +13454,7 @@
           <t>narrateur|Ava pose la balle dans la caisse. Elle classe. Catégorie des jouets.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13570,6 +13646,7 @@
           <t>narrateur|On peut prendre la pomme, la chaussette, ou le cube.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13738,6 +13815,7 @@
 narrateur|Jouets, c'est une catégorie. Elle a classé à le stand des jouets, dans la caisse. Papa dit merci.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13905,6 +13983,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14073,6 +14152,7 @@
 narrateur|Jouets, c'est une catégorie. Elle a classé à le stand des jouets, dans la caisse. Papa dit merci.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14240,6 +14320,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14408,6 +14489,7 @@
 narrateur|Jouets, c'est une catégorie. Elle a classé à le stand des jouets, dans la caisse. Papa dit merci.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14575,6 +14657,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14742,6 +14825,7 @@
           <t>narrateur|Ava glisse le livre dans le sac. Elle nomme. Elle classe. Une catégorie.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14933,6 +15017,7 @@
           <t>narrateur|On peut prendre la pomme, la chaussette, ou le cube.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15101,6 +15186,7 @@
 narrateur|Jouets, c'est une catégorie. Elle a classé à le stand des jouets, dans le sac. Papa dit merci.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15268,6 +15354,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15436,6 +15523,7 @@
 narrateur|Jouets, c'est une catégorie. Elle a classé à le stand des jouets, dans le sac. Papa dit merci.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15603,6 +15691,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15771,6 +15860,7 @@
 narrateur|Jouets, c'est une catégorie. Elle a classé à le stand des jouets, dans le sac. Papa dit merci.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15938,6 +16028,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15956,7 +16047,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15994,6 +16085,20 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -16008,7 +16113,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16195,6 +16300,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
